--- a/analise_logs.xlsx
+++ b/analise_logs.xlsx
@@ -99,13 +99,35 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:Z2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="20.40" customWidth="1"/>
+    <col min="1" max="1" width="45.70" customWidth="1"/>
     <col min="2" max="2" width="13.50" customWidth="1"/>
-    <col min="3" max="3" width="18.10" customWidth="1"/>
-    <col min="4" max="4" width="29.60" customWidth="1"/>
+    <col min="3" max="3" width="13.50" customWidth="1"/>
+    <col min="4" max="4" width="23.85" customWidth="1"/>
+    <col min="5" max="5" width="22.70" customWidth="1"/>
+    <col min="6" max="6" width="23.85" customWidth="1"/>
+    <col min="7" max="7" width="18.10" customWidth="1"/>
+    <col min="8" max="8" width="15.80" customWidth="1"/>
+    <col min="9" max="9" width="30.75" customWidth="1"/>
+    <col min="10" max="10" width="27.30" customWidth="1"/>
+    <col min="11" max="11" width="33.05" customWidth="1"/>
+    <col min="12" max="12" width="26.15" customWidth="1"/>
+    <col min="13" max="13" width="39.95" customWidth="1"/>
+    <col min="14" max="14" width="46.85" customWidth="1"/>
+    <col min="15" max="15" width="35.35" customWidth="1"/>
+    <col min="16" max="16" width="31.90" customWidth="1"/>
+    <col min="17" max="17" width="37.65" customWidth="1"/>
+    <col min="18" max="18" width="30.75" customWidth="1"/>
+    <col min="19" max="19" width="39.95" customWidth="1"/>
+    <col min="20" max="20" width="36.50" customWidth="1"/>
+    <col min="21" max="21" width="42.25" customWidth="1"/>
+    <col min="22" max="22" width="35.35" customWidth="1"/>
+    <col min="23" max="23" width="65.25" customWidth="1"/>
+    <col min="24" max="24" width="72.15" customWidth="1"/>
+    <col min="25" max="25" width="62.95" customWidth="1"/>
+    <col min="26" max="26" width="69.85" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -129,11 +151,121 @@
           <t xml:space="preserve">header_3</t>
         </is>
       </c>
+      <c r="E1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">header_4</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">header_5</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">header_6</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">header_7</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">header_8</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">header_9</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">header_10</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">header_11</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">header_12</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">header_13</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">header_14</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">header_15</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">header_16</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">header_17</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">header_18</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">header_19</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">header_20</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">header_21</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">header_22</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">header_23</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">header_24</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">header_25</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SPPVBRK.txt</t>
+          <t xml:space="preserve">ResourceStats_SPPNBRK_SPPNT999_JVM.txt</t>
         </is>
       </c>
       <c r="B2" t="inlineStr" s="2">
@@ -143,34 +275,122 @@
       </c>
       <c r="C2" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">BrokerUUID</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ExecutionGroupLabel</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ExecutionGroupUUID</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CollectionTimestamp</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">StartTimestamp</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">summary_NumberOfSessions</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">SPPVBRK_ODBC.txt</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">BrokerName</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">StartTimestamp</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">summary_NumberOfSessions</t>
+      <c r="H2" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EndTimeStamp</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">summary_InitialMemoryInMB</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">summary_UsedMemoryInMB</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">summary_CommittedMemoryInMB</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">summary_MaxMemoryInMB</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">summary_CumulativeGCTimeInSeconds</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">summary_CumulativeNumberOfGCCollections</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Heap Memory_InitialMemoryInMB</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Heap Memory_UsedMemoryInMB</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Heap Memory_CommittedMemoryInMB</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Heap Memory_MaxMemoryInMB</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Non-Heap Memory_InitialMemoryInMB</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Non-Heap Memory_UsedMemoryInMB</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Non-Heap Memory_CommittedMemoryInMB</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Non-Heap Memory_MaxMemoryInMB</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Garbage Collection - scavenge_CumulativeGCTimeInSeconds</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Garbage Collection - scavenge_CumulativeNumberOfGCCollections</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Garbage Collection - global_CumulativeGCTimeInSeconds</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Garbage Collection - global_CumulativeNumberOfGCCollections</t>
         </is>
       </c>
     </row>
@@ -180,13 +400,14 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:E26"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="29.60" customWidth="1"/>
+    <col min="1" max="1" width="72.15" customWidth="1"/>
     <col min="2" max="2" width="12.35" customWidth="1"/>
     <col min="3" max="3" width="18.10" customWidth="1"/>
-    <col min="4" max="4" width="34.20" customWidth="1"/>
+    <col min="4" max="4" width="45.70" customWidth="1"/>
+    <col min="5" max="5" width="76.75" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -207,6 +428,11 @@
       </c>
       <c r="D1" t="inlineStr" s="1">
         <is>
+          <t xml:space="preserve">arquivo exemplo</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr" s="1">
+        <is>
           <t xml:space="preserve">resumo</t>
         </is>
       </c>
@@ -218,50 +444,571 @@
         </is>
       </c>
       <c r="B2" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C2" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D2" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">BrokerName;2/2</t>
+          <t xml:space="preserve">ResourceStats_SPPNBRK_SPPNT999_JVM.txt</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">BrokerName;1/1</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">StartTimestamp</t>
+          <t xml:space="preserve">BrokerUUID</t>
         </is>
       </c>
       <c r="B3" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C3" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D3" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">StartTimestamp;2/2</t>
+          <t xml:space="preserve">ResourceStats_SPPNBRK_SPPNT999_JVM.txt</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">BrokerUUID;1/1</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">summary_NumberOfSessions</t>
+          <t xml:space="preserve">CollectionTimestamp</t>
         </is>
       </c>
       <c r="B4" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C4" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D4" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">summary_NumberOfSessions;2/2</t>
+          <t xml:space="preserve">ResourceStats_SPPNBRK_SPPNT999_JVM.txt</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CollectionTimestamp;1/1</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">EndTimeStamp</t>
+        </is>
+      </c>
+      <c r="B5" s="3">
+        <v>1</v>
+      </c>
+      <c r="C5" s="3">
+        <v>1</v>
+      </c>
+      <c r="D5" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">ResourceStats_SPPNBRK_SPPNT999_JVM.txt</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">EndTimeStamp;1/1</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ExecutionGroupLabel</t>
+        </is>
+      </c>
+      <c r="B6" s="2">
+        <v>1</v>
+      </c>
+      <c r="C6" s="2">
+        <v>1</v>
+      </c>
+      <c r="D6" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ResourceStats_SPPNBRK_SPPNT999_JVM.txt</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ExecutionGroupLabel;1/1</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">ExecutionGroupUUID</t>
+        </is>
+      </c>
+      <c r="B7" s="3">
+        <v>1</v>
+      </c>
+      <c r="C7" s="3">
+        <v>1</v>
+      </c>
+      <c r="D7" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">ResourceStats_SPPNBRK_SPPNT999_JVM.txt</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">ExecutionGroupUUID;1/1</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Garbage Collection - global_CumulativeGCTimeInSeconds</t>
+        </is>
+      </c>
+      <c r="B8" s="2">
+        <v>1</v>
+      </c>
+      <c r="C8" s="2">
+        <v>1</v>
+      </c>
+      <c r="D8" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ResourceStats_SPPNBRK_SPPNT999_JVM.txt</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Garbage Collection - global_CumulativeGCTimeInSeconds;1/1</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">Garbage Collection - global_CumulativeNumberOfGCCollections</t>
+        </is>
+      </c>
+      <c r="B9" s="3">
+        <v>1</v>
+      </c>
+      <c r="C9" s="3">
+        <v>1</v>
+      </c>
+      <c r="D9" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">ResourceStats_SPPNBRK_SPPNT999_JVM.txt</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">Garbage Collection - global_CumulativeNumberOfGCCollections;1/1</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Garbage Collection - scavenge_CumulativeGCTimeInSeconds</t>
+        </is>
+      </c>
+      <c r="B10" s="2">
+        <v>1</v>
+      </c>
+      <c r="C10" s="2">
+        <v>1</v>
+      </c>
+      <c r="D10" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ResourceStats_SPPNBRK_SPPNT999_JVM.txt</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Garbage Collection - scavenge_CumulativeGCTimeInSeconds;1/1</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">Garbage Collection - scavenge_CumulativeNumberOfGCCollections</t>
+        </is>
+      </c>
+      <c r="B11" s="3">
+        <v>1</v>
+      </c>
+      <c r="C11" s="3">
+        <v>1</v>
+      </c>
+      <c r="D11" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">ResourceStats_SPPNBRK_SPPNT999_JVM.txt</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">Garbage Collection - scavenge_CumulativeNumberOfGCCollections;1/1</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Heap Memory_CommittedMemoryInMB</t>
+        </is>
+      </c>
+      <c r="B12" s="2">
+        <v>1</v>
+      </c>
+      <c r="C12" s="2">
+        <v>1</v>
+      </c>
+      <c r="D12" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ResourceStats_SPPNBRK_SPPNT999_JVM.txt</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Heap Memory_CommittedMemoryInMB;1/1</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">Heap Memory_InitialMemoryInMB</t>
+        </is>
+      </c>
+      <c r="B13" s="3">
+        <v>1</v>
+      </c>
+      <c r="C13" s="3">
+        <v>1</v>
+      </c>
+      <c r="D13" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">ResourceStats_SPPNBRK_SPPNT999_JVM.txt</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">Heap Memory_InitialMemoryInMB;1/1</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Heap Memory_MaxMemoryInMB</t>
+        </is>
+      </c>
+      <c r="B14" s="2">
+        <v>1</v>
+      </c>
+      <c r="C14" s="2">
+        <v>1</v>
+      </c>
+      <c r="D14" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ResourceStats_SPPNBRK_SPPNT999_JVM.txt</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Heap Memory_MaxMemoryInMB;1/1</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">Heap Memory_UsedMemoryInMB</t>
+        </is>
+      </c>
+      <c r="B15" s="3">
+        <v>1</v>
+      </c>
+      <c r="C15" s="3">
+        <v>1</v>
+      </c>
+      <c r="D15" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">ResourceStats_SPPNBRK_SPPNT999_JVM.txt</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">Heap Memory_UsedMemoryInMB;1/1</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Non-Heap Memory_CommittedMemoryInMB</t>
+        </is>
+      </c>
+      <c r="B16" s="2">
+        <v>1</v>
+      </c>
+      <c r="C16" s="2">
+        <v>1</v>
+      </c>
+      <c r="D16" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ResourceStats_SPPNBRK_SPPNT999_JVM.txt</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Non-Heap Memory_CommittedMemoryInMB;1/1</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">Non-Heap Memory_InitialMemoryInMB</t>
+        </is>
+      </c>
+      <c r="B17" s="3">
+        <v>1</v>
+      </c>
+      <c r="C17" s="3">
+        <v>1</v>
+      </c>
+      <c r="D17" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">ResourceStats_SPPNBRK_SPPNT999_JVM.txt</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">Non-Heap Memory_InitialMemoryInMB;1/1</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Non-Heap Memory_MaxMemoryInMB</t>
+        </is>
+      </c>
+      <c r="B18" s="2">
+        <v>1</v>
+      </c>
+      <c r="C18" s="2">
+        <v>1</v>
+      </c>
+      <c r="D18" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ResourceStats_SPPNBRK_SPPNT999_JVM.txt</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">Non-Heap Memory_MaxMemoryInMB;1/1</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">Non-Heap Memory_UsedMemoryInMB</t>
+        </is>
+      </c>
+      <c r="B19" s="3">
+        <v>1</v>
+      </c>
+      <c r="C19" s="3">
+        <v>1</v>
+      </c>
+      <c r="D19" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">ResourceStats_SPPNBRK_SPPNT999_JVM.txt</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">Non-Heap Memory_UsedMemoryInMB;1/1</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">StartTimestamp</t>
+        </is>
+      </c>
+      <c r="B20" s="2">
+        <v>1</v>
+      </c>
+      <c r="C20" s="2">
+        <v>1</v>
+      </c>
+      <c r="D20" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ResourceStats_SPPNBRK_SPPNT999_JVM.txt</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">StartTimestamp;1/1</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">summary_CommittedMemoryInMB</t>
+        </is>
+      </c>
+      <c r="B21" s="3">
+        <v>1</v>
+      </c>
+      <c r="C21" s="3">
+        <v>1</v>
+      </c>
+      <c r="D21" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">ResourceStats_SPPNBRK_SPPNT999_JVM.txt</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">summary_CommittedMemoryInMB;1/1</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">summary_CumulativeGCTimeInSeconds</t>
+        </is>
+      </c>
+      <c r="B22" s="2">
+        <v>1</v>
+      </c>
+      <c r="C22" s="2">
+        <v>1</v>
+      </c>
+      <c r="D22" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ResourceStats_SPPNBRK_SPPNT999_JVM.txt</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">summary_CumulativeGCTimeInSeconds;1/1</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">summary_CumulativeNumberOfGCCollections</t>
+        </is>
+      </c>
+      <c r="B23" s="3">
+        <v>1</v>
+      </c>
+      <c r="C23" s="3">
+        <v>1</v>
+      </c>
+      <c r="D23" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">ResourceStats_SPPNBRK_SPPNT999_JVM.txt</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">summary_CumulativeNumberOfGCCollections;1/1</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">summary_InitialMemoryInMB</t>
+        </is>
+      </c>
+      <c r="B24" s="2">
+        <v>1</v>
+      </c>
+      <c r="C24" s="2">
+        <v>1</v>
+      </c>
+      <c r="D24" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ResourceStats_SPPNBRK_SPPNT999_JVM.txt</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">summary_InitialMemoryInMB;1/1</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">summary_MaxMemoryInMB</t>
+        </is>
+      </c>
+      <c r="B25" s="3">
+        <v>1</v>
+      </c>
+      <c r="C25" s="3">
+        <v>1</v>
+      </c>
+      <c r="D25" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">ResourceStats_SPPNBRK_SPPNT999_JVM.txt</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">summary_MaxMemoryInMB;1/1</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">summary_UsedMemoryInMB</t>
+        </is>
+      </c>
+      <c r="B26" s="2">
+        <v>1</v>
+      </c>
+      <c r="C26" s="2">
+        <v>1</v>
+      </c>
+      <c r="D26" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ResourceStats_SPPNBRK_SPPNT999_JVM.txt</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">summary_UsedMemoryInMB;1/1</t>
         </is>
       </c>
     </row>
@@ -297,7 +1044,7 @@
         </is>
       </c>
       <c r="B2" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -307,7 +1054,7 @@
         </is>
       </c>
       <c r="B3" s="3">
-        <v>3</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>
